--- a/public/cvdocus/bewerbungen.xlsx
+++ b/public/cvdocus/bewerbungen.xlsx
@@ -11,12 +11,15 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$98</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="249">
   <si>
     <t>Benennung der Stelle</t>
   </si>
@@ -99,9 +102,6 @@
     <t>Better Sell Online GmbH</t>
   </si>
   <si>
-    <t>30 Hannover, Deutschland</t>
-  </si>
-  <si>
     <t>Frontend Entwickler (m/w/d)</t>
   </si>
   <si>
@@ -186,9 +186,6 @@
     <t>Frontend Developer - Energy Infrastructure </t>
   </si>
   <si>
-    <t>91154 Roth</t>
-  </si>
-  <si>
     <t>edison street GmbH</t>
   </si>
   <si>
@@ -307,13 +304,475 @@
   </si>
   <si>
     <t xml:space="preserve">Ehrhardt + Partner Group </t>
+  </si>
+  <si>
+    <t>PHP Software-Entwickler / Symfony Developer</t>
+  </si>
+  <si>
+    <t>GO! Express &amp; Logistics GmbH</t>
+  </si>
+  <si>
+    <t>APRIORI Experts GmbH</t>
+  </si>
+  <si>
+    <t>Full-Stack-Entwickler C# / React (m/w/d)</t>
+  </si>
+  <si>
+    <t>Regensburg</t>
+  </si>
+  <si>
+    <t>Hochschule Weihestephan-Triesdorf</t>
+  </si>
+  <si>
+    <t>91737 Weidenbach</t>
+  </si>
+  <si>
+    <t>Web-Entwickler Initiativbewerbung</t>
+  </si>
+  <si>
+    <t>APROVIS Energy Systems GmbH</t>
+  </si>
+  <si>
+    <t>Softwareentwickler/Programierer</t>
+  </si>
+  <si>
+    <t>Jura Direkt GmbH</t>
+  </si>
+  <si>
+    <t>UX Engineer / Frontend Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Software-Entwickler Frontend Firmenkunden (m/w/d)</t>
+  </si>
+  <si>
+    <t>Finanz Informatik GmbH &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>Java-Script und UI-Entwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Full Stack Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Ansbach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ipi GmbH </t>
+  </si>
+  <si>
+    <t>Junior Frontend Entwickler (m/w/d</t>
+  </si>
+  <si>
+    <t>Wermelskirchen bei Köln</t>
+  </si>
+  <si>
+    <t>Veritreff GmbH</t>
+  </si>
+  <si>
+    <t>Low Code Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>BearingPoint GmbH</t>
+  </si>
+  <si>
+    <t>München, Stuttgart, Berlin</t>
+  </si>
+  <si>
+    <t>Softwarearchitekt (m/w/d) - Smart Farming/</t>
+  </si>
+  <si>
+    <t>Loiching, remote bundesweit</t>
+  </si>
+  <si>
+    <t>Sano - Moderne Tierernährung GmbH</t>
+  </si>
+  <si>
+    <t>IT-Consultant / Business Analyst (m/w/d)</t>
+  </si>
+  <si>
+    <t>Avision GmbH</t>
+  </si>
+  <si>
+    <t>Web-Entwickler Frontend </t>
+  </si>
+  <si>
+    <t>Trainee Anwendungsberatung (m/w/d) für Finanzsoftware</t>
+  </si>
+  <si>
+    <t>Ostfildern</t>
+  </si>
+  <si>
+    <t>Simba Computer Systeme GmbH</t>
+  </si>
+  <si>
+    <t>Hutter &amp; Unger GmbH</t>
+  </si>
+  <si>
+    <t>Technischer Assistent in Voll- oder Teilzeit (m/w/d)</t>
+  </si>
+  <si>
+    <t>IT-Fachkraft // Technischer Sachbearbeiter</t>
+  </si>
+  <si>
+    <t>Igling</t>
+  </si>
+  <si>
+    <t>Berufsstarter Agile Softwareentwicklung (m/w/d)</t>
+  </si>
+  <si>
+    <t>andrena objects ag</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hannover, Deutschland</t>
+  </si>
+  <si>
+    <t>Roth</t>
+  </si>
+  <si>
+    <t>Wertingen</t>
+  </si>
+  <si>
+    <t>OPTITOOL GmbH</t>
+  </si>
+  <si>
+    <t>[OT-DW] Web-Entwickler / Web Developer (m/w/d) in Vollzeit</t>
+  </si>
+  <si>
+    <t>Baist GmbH</t>
+  </si>
+  <si>
+    <t>Ludwigshafen am Rhein</t>
+  </si>
+  <si>
+    <t>Webdesigner/Webentwickler/Webdeveloper (w/m/d)</t>
+  </si>
+  <si>
+    <t>Web Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>eddyson GmbH</t>
+  </si>
+  <si>
+    <t>Göttingen</t>
+  </si>
+  <si>
+    <t>Junior Low-Code-Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>SCOPELAND Technology GmbH</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>Web Developer (w/m/d) - Web</t>
+  </si>
+  <si>
+    <t>Johanngeorgenstadt</t>
+  </si>
+  <si>
+    <t>Stadt Johanngeorgenstadt</t>
+  </si>
+  <si>
+    <t>Frontend Webentwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>4eBusiness GmbH</t>
+  </si>
+  <si>
+    <t>Entwickler Webtechnology (m/w/d)</t>
+  </si>
+  <si>
+    <t>sirconic group GmbH</t>
+  </si>
+  <si>
+    <t>Freilassing</t>
+  </si>
+  <si>
+    <t>Ingenieur Verfahrens- &amp; Prozesstechnik (m/w/d)</t>
+  </si>
+  <si>
+    <t>FERCHAU – Connecting People and Technologies</t>
+  </si>
+  <si>
+    <t>Junior Frontend Developer - E-Commerce / Shopify (m/w/d)</t>
+  </si>
+  <si>
+    <t>ABRIO GmbH c/o WeWork</t>
+  </si>
+  <si>
+    <t>Webentwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Landshut</t>
+  </si>
+  <si>
+    <t>XPECTO AG</t>
+  </si>
+  <si>
+    <t>Frontend-Entwickler (w/m/d)</t>
+  </si>
+  <si>
+    <t>Cottbus</t>
+  </si>
+  <si>
+    <t>Migrando GmbH</t>
+  </si>
+  <si>
+    <t>ReactJS Specialist (m/w/d)</t>
+  </si>
+  <si>
+    <t>Bezirk Neukölln, Berlin,</t>
+  </si>
+  <si>
+    <t>list&amp;sell GmbH</t>
+  </si>
+  <si>
+    <t>Frontend Developer im Cloud-Umfeld (m/w/d)</t>
+  </si>
+  <si>
+    <t>Weiterstadt</t>
+  </si>
+  <si>
+    <t>holos supply GmbH</t>
+  </si>
+  <si>
+    <t>Traumjob Entwickler</t>
+  </si>
+  <si>
+    <t>Reichenbach</t>
+  </si>
+  <si>
+    <t>2peaches GmbH</t>
+  </si>
+  <si>
+    <t>Junior Softwareentwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Gate4 GmbH</t>
+  </si>
+  <si>
+    <t>Bonn</t>
+  </si>
+  <si>
+    <t>Frontend Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Taunusstein</t>
+  </si>
+  <si>
+    <t>Brita</t>
+  </si>
+  <si>
+    <t>Junior Frontend Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Audio Factory Media GmbH</t>
+  </si>
+  <si>
+    <t>Westerkappeln</t>
+  </si>
+  <si>
+    <t>Foto Erhardt GmbH</t>
+  </si>
+  <si>
+    <t>Frontend Webentwickler/-in (m/w/d)</t>
+  </si>
+  <si>
+    <t>Ulm, Donau</t>
+  </si>
+  <si>
+    <t>ProDigital Consulting GmbH</t>
+  </si>
+  <si>
+    <t>Softwareentwickler Frontend (m/w/d)</t>
+  </si>
+  <si>
+    <t>Wolpertshausen</t>
+  </si>
+  <si>
+    <t>iPLON Solutions</t>
+  </si>
+  <si>
+    <t>Frontend-Entwickler/Frontend-Entwicklerin (m/w/d)</t>
+  </si>
+  <si>
+    <t>stiftung elektro-altgeräte register</t>
+  </si>
+  <si>
+    <t>Coburg, Gotha, Bundesweit</t>
+  </si>
+  <si>
+    <t>FIDA</t>
+  </si>
+  <si>
+    <t>Neumarkt in der Oberpfalz</t>
+  </si>
+  <si>
+    <t>mr. pixel KG</t>
+  </si>
+  <si>
+    <t>Web-Entwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Frontend-Entwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>offizium/next</t>
+  </si>
+  <si>
+    <t>Bad Neustadt oder Würzburg</t>
+  </si>
+  <si>
+    <t>Job, Back-/Front End, Full Stack Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Ludwigsburg</t>
+  </si>
+  <si>
+    <t>K11 Rechtsanwaltsgesellschaft mbH</t>
+  </si>
+  <si>
+    <t>Softwareentwickler (w/m/d) - Frontend</t>
+  </si>
+  <si>
+    <t>Fürth</t>
+  </si>
+  <si>
+    <t>Brandad</t>
+  </si>
+  <si>
+    <t>Frontend Entwickler (m|w|d) Angular</t>
+  </si>
+  <si>
+    <t>Assecor GmbH</t>
+  </si>
+  <si>
+    <t> Frontend Developer - AI-gestützte Finance-Anwendungen (w/m/d)</t>
+  </si>
+  <si>
+    <t>Berlin, München</t>
+  </si>
+  <si>
+    <t>KPMG</t>
+  </si>
+  <si>
+    <t>Frontend Developer React / TypeScript (w/m/d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> in Stuttgart</t>
+  </si>
+  <si>
+    <t>SprintEins</t>
+  </si>
+  <si>
+    <t>Trainee Web Development</t>
+  </si>
+  <si>
+    <t>Gräfelfing</t>
+  </si>
+  <si>
+    <t>FUTRUE</t>
+  </si>
+  <si>
+    <t>Junior Web Developer (m/w/d) - Node.js / React</t>
+  </si>
+  <si>
+    <t>FinMent</t>
+  </si>
+  <si>
+    <t>Hachenburg</t>
+  </si>
+  <si>
+    <t>global office GmbH</t>
+  </si>
+  <si>
+    <t>consulting1x1 GmbH</t>
+  </si>
+  <si>
+    <t>Leverkusen</t>
+  </si>
+  <si>
+    <t>Frontend Developer (M/W/D)</t>
+  </si>
+  <si>
+    <t>Junior Software Entwickler Programm (m/w/d) - Frontend</t>
+  </si>
+  <si>
+    <t>BAUHAUS </t>
+  </si>
+  <si>
+    <t>Mannheim</t>
+  </si>
+  <si>
+    <t>Erlangen</t>
+  </si>
+  <si>
+    <t>parq parking GmbH</t>
+  </si>
+  <si>
+    <t>Junior Web Entwickler / Junior Web Developer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Bottrop</t>
+  </si>
+  <si>
+    <t>Vielfalter GmbH &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>LEWO Media</t>
+  </si>
+  <si>
+    <t>Trier</t>
+  </si>
+  <si>
+    <t>Full-Stack-Entwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>Kite IT GmbH</t>
+  </si>
+  <si>
+    <t>Frontend Developer / Typescript Engineer (m/w/d)</t>
+  </si>
+  <si>
+    <t>ADS Allgemeine Deutsche St.ber.ges.</t>
+  </si>
+  <si>
+    <t>governikus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Berlin, Kempten</t>
+  </si>
+  <si>
+    <t>uNaice GmbH</t>
+  </si>
+  <si>
+    <t>Remote (Deutschland)</t>
+  </si>
+  <si>
+    <t>Junior Full-Stack Developer befristet 2 Monate</t>
+  </si>
+  <si>
+    <t>Junior Frontend Developer für Shopify</t>
+  </si>
+  <si>
+    <t>Köln, Deutschland</t>
+  </si>
+  <si>
+    <t> AthariCommerce</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +801,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -490,6 +956,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -786,19 +1258,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
     <col min="2" max="2" width="67.44140625" customWidth="1"/>
     <col min="3" max="3" width="48.6640625" customWidth="1"/>
     <col min="4" max="4" width="41.44140625" customWidth="1"/>
     <col min="5" max="5" width="19.21875" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="4.77734375" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.8" customHeight="1" thickBot="1">
+    <row r="1" spans="1:9" ht="25.8" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -807,19 +1281,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -836,13 +1310,20 @@
         <v>46143</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>SUM(H2:H334)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -859,13 +1340,16 @@
         <v>46143</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -886,7 +1370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -907,7 +1391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -928,7 +1412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="7" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -949,7 +1433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="8" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -966,13 +1450,16 @@
         <v>46152</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="11">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -983,7 +1470,7 @@
         <v>26</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="E9" s="9">
         <v>46152</v>
@@ -993,64 +1480,70 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="10" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="E10" s="12">
         <v>46152</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="11">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A11" s="13">
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="E11" s="12">
         <v>46152</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="E12" s="9">
         <v>46152</v>
@@ -1060,18 +1553,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="13" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="E13" s="9">
         <v>46152</v>
@@ -1081,15 +1574,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="14" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A14" s="10">
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>19</v>
@@ -1098,24 +1591,27 @@
         <v>46156</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="11">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="E15" s="9">
         <v>46156</v>
@@ -1125,107 +1621,119 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="21" customHeight="1" thickBot="1">
+    <row r="16" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="E16" s="12">
         <v>46156</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G16" s="11">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A17" s="13">
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="E17" s="12">
         <v>46156</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G17" s="11">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="E18" s="12">
         <v>46156</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G18" s="11">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="E19" s="12">
         <v>46156</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="11">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A20" s="13">
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>19</v>
@@ -1234,71 +1742,79 @@
         <v>46156</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="11">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A21" s="10">
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="E21" s="12">
         <v>46159</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" s="11">
         <v>20</v>
       </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A22" s="13">
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="E22" s="12">
         <v>46159</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" s="11">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="21" customHeight="1" thickBot="1">
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="E23" s="9">
         <v>46159</v>
@@ -1308,61 +1824,67 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.600000000000001" thickBot="1">
+    <row r="24" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="D24" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E24" s="12">
         <v>46159</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" s="11">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A25" s="13">
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E25" s="12">
         <v>46167</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" s="11">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>19</v>
@@ -1371,93 +1893,105 @@
         <v>46167</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" s="11">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A27" s="10">
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="12">
         <v>46167</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" s="11">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A28" s="13">
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>83</v>
-      </c>
       <c r="D28" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E28" s="12">
         <v>46167</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" s="11">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A29" s="10">
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="12">
         <v>46167</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" s="11">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="18.600000000000001" thickBot="1">
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E30" s="9">
         <v>46167</v>
@@ -1467,18 +2001,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.600000000000001" thickBot="1">
+    <row r="31" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A31" s="5">
         <v>30</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E31" s="9">
         <v>46167</v>
@@ -1488,18 +2022,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.600000000000001" thickBot="1">
+    <row r="32" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="D32" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E32" s="9">
         <v>46167</v>
@@ -1509,39 +2043,1462 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18.600000000000001" thickBot="1">
-      <c r="A33" s="5">
+    <row r="33" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A33" s="10">
         <v>32</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="12">
+        <v>46168</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" s="11">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A34" s="10">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="12">
+        <v>46205</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" s="11">
+        <v>33</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A35" s="10">
+        <v>34</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="12">
+        <v>46205</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="11">
+        <v>34</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="9">
+        <v>46210</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A37" s="10">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="12">
+        <v>46211</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" s="11">
+        <v>36</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" s="9">
+        <v>46212</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="9">
+        <v>46212</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A40" s="10">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="12">
+        <v>46212</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="11">
+        <v>39</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A41" s="10">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="12">
+        <v>46212</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" s="11">
+        <v>40</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="9">
+        <v>46212</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" s="9">
+        <v>46213</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A44" s="10">
+        <v>43</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="12">
+        <v>46213</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" s="11">
+        <v>43</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" s="9">
+        <v>46213</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="9">
+        <v>46215</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="9">
+        <v>46215</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="9">
+        <v>46215</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="9">
+        <v>46215</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="9">
+        <v>46215</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A51" s="10">
+        <v>50</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="12">
+        <v>46216</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G51" s="11">
+        <v>50</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A52" s="10">
+        <v>51</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="12">
+        <v>46216</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G52" s="11">
+        <v>51</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" s="9">
+        <v>46216</v>
+      </c>
+      <c r="F53" s="17"/>
+      <c r="G53" s="7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" s="9">
+        <v>46216</v>
+      </c>
+      <c r="F54" s="17"/>
+      <c r="G54" s="7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A55" s="10">
+        <v>54</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="12">
+        <v>46216</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="11">
+        <v>54</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="9">
+        <v>46216</v>
+      </c>
+      <c r="F56" s="17"/>
+      <c r="G56" s="7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" s="9">
+        <v>46216</v>
+      </c>
+      <c r="F57" s="17"/>
+      <c r="G57" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" s="9">
+        <v>46216</v>
+      </c>
+      <c r="F58" s="17"/>
+      <c r="G58" s="7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="9">
+        <v>46218</v>
+      </c>
+      <c r="F59" s="17"/>
+      <c r="G59" s="7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A60" s="10">
+        <v>59</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E60" s="12">
+        <v>46218</v>
+      </c>
+      <c r="F60" s="18"/>
+      <c r="G60" s="11">
+        <v>59</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="9">
+        <v>46218</v>
+      </c>
+      <c r="F61" s="17"/>
+      <c r="G61" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E62" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F62" s="17"/>
+      <c r="G62" s="7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F63" s="17"/>
+      <c r="G63" s="7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A64" s="5">
+        <v>63</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F64" s="17"/>
+      <c r="G64" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F65" s="17"/>
+      <c r="G65" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E66" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A68" s="10">
+        <v>67</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E68" s="12">
+        <v>46223</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="11">
+        <v>67</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A69" s="10">
+        <v>68</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="12">
+        <v>46223</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G69" s="11">
+        <v>68</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" s="9">
+        <v>46223</v>
+      </c>
+      <c r="F70" s="17"/>
+      <c r="G70" s="7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E71" s="9">
+        <v>46223</v>
+      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F72" s="17"/>
+      <c r="G72" s="7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F73" s="17"/>
+      <c r="G73" s="7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A74" s="10">
+        <v>73</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" s="12">
+        <v>46224</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G74" s="11">
+        <v>73</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E75" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F75" s="17"/>
+      <c r="G75" s="7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F76" s="17"/>
+      <c r="G76" s="7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E77" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F77" s="17"/>
+      <c r="G77" s="7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" s="9">
+        <v>46224</v>
+      </c>
+      <c r="F78" s="17"/>
+      <c r="G78" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A79" s="10">
+        <v>78</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E79" s="12">
+        <v>46226</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G79" s="11">
+        <v>78</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A80" s="10">
+        <v>79</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" s="12">
+        <v>46227</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G80" s="11">
+        <v>79</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A81" s="10">
+        <v>80</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="12">
+        <v>46227</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" s="11">
+        <v>80</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A82" s="10">
+        <v>81</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E82" s="12">
+        <v>46227</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G82" s="11">
+        <v>81</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A83" s="10">
+        <v>82</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E83" s="12">
+        <v>46227</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G83" s="11">
+        <v>82</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E84" s="9">
+        <v>46228</v>
+      </c>
+      <c r="F84" s="17"/>
+      <c r="G84" s="7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" s="9">
+        <v>46228</v>
+      </c>
+      <c r="F85" s="17"/>
+      <c r="G85" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="9">
+        <v>46228</v>
+      </c>
+      <c r="F86" s="17"/>
+      <c r="G86" s="7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E87" s="9">
+        <v>46229</v>
+      </c>
+      <c r="F87" s="17"/>
+      <c r="G87" s="7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E88" s="9">
+        <v>46229</v>
+      </c>
+      <c r="F88" s="17"/>
+      <c r="G88" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="9">
+        <v>46229</v>
+      </c>
+      <c r="F89" s="17"/>
+      <c r="G89" s="7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E90" s="9">
+        <v>46230</v>
+      </c>
+      <c r="F90" s="17"/>
+      <c r="G90" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A91" s="10">
+        <v>90</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E91" s="12">
+        <v>46230</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="11">
+        <v>90</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E92" s="9">
+        <v>46230</v>
+      </c>
+      <c r="F92" s="17"/>
+      <c r="G92" s="7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A93" s="10">
+        <v>92</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E93" s="12">
+        <v>46230</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" s="11">
+        <v>92</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A94" s="10">
+        <v>93</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E94" s="12">
+        <v>46231</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="11">
+        <v>93</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="9">
-        <v>46168</v>
-      </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="18.600000000000001" thickBot="1">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="7"/>
+    </row>
+    <row r="97" spans="1:7" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="B97" s="16"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" spans="1:7" ht="20.399999999999999" customHeight="1" thickBot="1">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
+      <c r="B98" s="16"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="17"/>
+      <c r="G98" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D98"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" location="location" display="https://www.stepstone.de/stellenangebote--Frontend-Entwickler-w-m-d-als-Elternzeitvertretung-Hannover-HIS-Hochschul-Informations-System-eG--13969803-inline.html - location"/>
     <hyperlink ref="D3" r:id="rId2" location="location" display="https://www.stepstone.de/stellenangebote--Trainee-m-w-d-UX-UI-Design-Frontend-Development-Neuss-bei-Duesseldorf-Bank11-fuer-Privatkunden-und-Handel-GmbH--13904930-inline.html?rltr=6_6_25_seorl_m_1_0_0_0_0_0 - location"/>
@@ -1554,9 +3511,16 @@
     <hyperlink ref="D28" r:id="rId9" location="location" display="https://www.stepstone.de/stellenangebote--Frontend-Software-Engineer-m-w-d-Trading-Analytics-Tools-React-TypeScript-Oststeinbek-SSW-Trading-GmbH--13941349-inline.html - location"/>
     <hyperlink ref="C30" r:id="rId10" display="https://talents.studysmarter.de/companies/zero-to-one-search/"/>
     <hyperlink ref="D30" r:id="rId11" location="location" display="https://www.stepstone.de/stellenangebote--Junior-Produktmanager-m-w-d-UX-UI-AI-Experience-Mietwagen-Augsburg-CHECK24--14049234-inline.html - location"/>
+    <hyperlink ref="D43" r:id="rId12" location="location" display="https://www.stepstone.de/stellenangebote--Junior-Frontend-Entwickler-m-w-d-Wermelskirchen-bei-Koeln-Veritreff-GmbH--14171376-inline.html - location"/>
+    <hyperlink ref="D45" r:id="rId13" location="location" display="https://www.stepstone.de/stellenangebote--Softwarearchitekt-Smart-Farming-Datenanalyse-KI-m-w-d-Loiching-remote-bundesweit-Sano-Moderne-Tierernaehrung-GmbH--14244849-inline.html?rltr=3_3_25_seorl_m_0_0_0_0_1_0 - location"/>
+    <hyperlink ref="B51" r:id="rId14" display="https://www.stepstone.de/stellenangebote--Berufsstarter-Agile-Softwareentwicklung-m-w-d-Frankfurt-am-Main-andrena-objects-ag--13409341-inline.html"/>
+    <hyperlink ref="C75" r:id="rId15" display="https://de.indeed.com/cmp/Mr.-Pixel-Kg?campaignid=mobvjcmp&amp;from=mobviewjob&amp;tk=1ju2f34b6hceg802&amp;fromjk=239a874cee4156e3"/>
+    <hyperlink ref="C87" r:id="rId16" display="https://join.com/companies/parq-parkingcom"/>
+    <hyperlink ref="C88" r:id="rId17" display="https://join.com/companies/vielfalter"/>
+    <hyperlink ref="D94" r:id="rId18" display="https://www.google.com/maps/search/?api=1&amp;query=K%C3%B6ln%20%28Nordrhein-Westfalen%29%2C%20Deutschland"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
 
